--- a/software_developer_forms/009_fintech_software_engineer_job_application--software_developer_forms.xlsx
+++ b/software_developer_forms/009_fintech_software_engineer_job_application--software_developer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_41,_'name':_'bachelor',_'label':_'bachelor',_'value':_'bachelor',_'options':_[{'id':_51,_'name':_'degree',_'label':_'degree',_'value':_'degree'},_{'id':_52,_'name':_'diploma',_'label':_'diploma',_'value':_'diploma'},_{'id':_53,_'name':_'certificate',_'label':_'certificate',_'value':_'certificate'},_{'id':_54,_'name':_'associate',_'label':_'associate',_'value':_'associate'}]}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 41, 'name': 'bachelor', 'label': 'Bachelor', 'value': 'bachelor', 'options': [{'id': 51, 'name': 'degree', 'label': 'Degree', 'value': 'degree'}, {'id': 52, 'name': 'diploma', 'label': 'Diploma', 'value': 'diploma'}, {'id': 53, 'name': 'certificate', 'label': 'Certificate', 'value': 'certificate'}, {'id': 54, 'name': 'associate', 'label': 'Associate', 'value': 'associate'}]}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_42,_'name':_'master',_'label':_'master',_'value':_'master',_'options':_[{'id':_55,_'name':_'degree',_'label':_'degree',_'value':_'degree'},_{'id':_56,_'name':_'diploma',_'label':_'diploma',_'value':_'diploma'},_{'id':_57,_'name':_'certificate',_'label':_'certificate',_'value':_'certificate'},_{'id':_58,_'name':_'associate',_'label':_'associate',_'value':_'associate'}]}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 42, 'name': 'master', 'label': 'Master', 'value': 'master', 'options': [{'id': 55, 'name': 'degree', 'label': 'Degree', 'value': 'degree'}, {'id': 56, 'name': 'diploma', 'label': 'Diploma', 'value': 'diploma'}, {'id': 57, 'name': 'certificate', 'label': 'Certificate', 'value': 'certificate'}, {'id': 58, 'name': 'associate', 'label': 'Associate', 'value': 'associate'}]}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'work_experience',_'label':_'work_experience',_'hint':_none,_'type':_'date',_'required':_true,_'options':_[]}</t>
+          <t>work_experience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'work_experience', 'label': 'Work Experience', 'hint': None, 'type': 'date', 'required': True, 'options': []}</t>
+          <t>Work Experience</t>
         </is>
       </c>
     </row>
